--- a/output/pdf_financials_xlsx/NOBL.xlsx
+++ b/output/pdf_financials_xlsx/NOBL.xlsx
@@ -5994,19 +5994,19 @@
         <v>0.805069</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.278812</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.278812</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.506542</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.506542</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.728893</v>
       </c>
     </row>
     <row r="93">
@@ -6614,10 +6614,10 @@
         <v>-0.048585</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>0.034945</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>-0.007158</v>
       </c>
     </row>
     <row r="104">
@@ -6788,10 +6788,10 @@
         <v>-0.06938</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.039224</v>
+        <v>-0.004279</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.008623</v>
+        <v>0.001465</v>
       </c>
     </row>
     <row r="107">
@@ -7475,19 +7475,19 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.734228</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>1.145349</v>
+        <v>1.09694</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.132348</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.282612</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.768763</v>
       </c>
     </row>
     <row r="119">
@@ -9821,7 +9821,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10797,7 +10801,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -16702,7 +16710,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17070,7 +17082,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -20062,7 +20078,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -22755,7 +22775,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOBL.xlsx
+++ b/output/pdf_financials_xlsx/NOBL.xlsx
@@ -1029,25 +1029,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000967</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000395</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002305</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.015955</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.016636</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000974</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000684</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.005065</v>
       </c>
     </row>
     <row r="13">
@@ -1983,25 +1983,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.058077</v>
+        <v>-0.059044</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.233636</v>
+        <v>-0.234031</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.864322</v>
+        <v>-1.866627</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.895496</v>
+        <v>-1.911451</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.892282</v>
+        <v>-0.908918</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.260893</v>
+        <v>-1.261867</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.302178</v>
+        <v>-2.302862</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.137054</v>
@@ -2031,7 +2031,7 @@
         <v>-0.518343</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.663421</v>
+        <v>-0.668486</v>
       </c>
     </row>
     <row r="28">
@@ -2099,25 +2099,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.058077</v>
+        <v>-0.059044</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.233636</v>
+        <v>-0.234031</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.864322</v>
+        <v>-1.866627</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.871091</v>
+        <v>-1.887046</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.876594</v>
+        <v>-0.89323</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.250265</v>
+        <v>-1.251239</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.296364</v>
+        <v>-2.297048</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.134647</v>
@@ -2147,7 +2147,7 @@
         <v>-0.518343</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.663421</v>
+        <v>-0.668486</v>
       </c>
     </row>
     <row r="30">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.11048</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.036214</v>
@@ -2430,31 +2430,31 @@
         <v>0.142784</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.228021</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.064848</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.109757</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.057675</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.031647</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.065104</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.743336</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.19975</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.346226</v>
       </c>
     </row>
     <row r="35">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.11048</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.036214</v>
@@ -2546,31 +2546,31 @@
         <v>0.142784</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.228021</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.064848</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.109757</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.057675</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.031647</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.065104</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.743336</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.19975</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.346226</v>
       </c>
     </row>
     <row r="37">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.123704</v>
+        <v>0.013224</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -3242,31 +3242,31 @@
         <v>0.000679</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.231394</v>
+        <v>0.003373</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.071731</v>
+        <v>0.006883</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.11254</v>
+        <v>0.002783</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.063234</v>
+        <v>0.005559</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.03736</v>
+        <v>0.005713</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.065815</v>
+        <v>0.000711</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.7993209999999999</v>
+        <v>0.055985</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.236072</v>
+        <v>0.036322</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.377362</v>
+        <v>0.031136</v>
       </c>
     </row>
     <row r="49">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -40402,7 +40402,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -41059,7 +41059,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -41346,7 +41346,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -41946,7 +41946,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -45336,7 +45336,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -48667,7 +48667,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" s="5" t="n">

--- a/output/pdf_financials_xlsx/NOBL.xlsx
+++ b/output/pdf_financials_xlsx/NOBL.xlsx
@@ -4234,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.039634</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.084079</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.090544</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013224</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.01006</v>
@@ -7042,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024916</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038896</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -8422,10 +8422,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024916</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038896</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>-0.526066</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.814581</v>
+        <v>-0.839497</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -26757,7 +26757,11 @@
           <t>Issuance of shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -30020,7 +30024,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -30727,7 +30735,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -31226,7 +31238,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -35088,7 +35104,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -38332,7 +38352,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="n">
         <v>-0.013224</v>
       </c>
@@ -48964,7 +48988,11 @@
           <t>Future income tax recovery 7</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -50271,7 +50299,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
